--- a/output/yearly_population_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_10_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6603</v>
+        <v>5964</v>
       </c>
       <c r="C2" t="n">
-        <v>11233</v>
+        <v>12322</v>
       </c>
       <c r="D2" t="n">
-        <v>20994</v>
+        <v>34788</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3049</v>
+        <v>3947</v>
       </c>
       <c r="C3" t="n">
-        <v>4942</v>
+        <v>5400</v>
       </c>
       <c r="D3" t="n">
-        <v>12523</v>
+        <v>14682</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2608</v>
+        <v>2926</v>
       </c>
       <c r="C4" t="n">
-        <v>5067</v>
+        <v>5418</v>
       </c>
       <c r="D4" t="n">
-        <v>6619</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1820</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>4157</v>
+        <v>4871</v>
       </c>
       <c r="D5" t="n">
-        <v>2759</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C6" t="n">
-        <v>3045</v>
+        <v>3714</v>
       </c>
       <c r="D6" t="n">
-        <v>1157</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>519</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
-        <v>1899</v>
+        <v>2438</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>965</v>
+        <v>1234</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>496</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7278</v>
+        <v>7435</v>
       </c>
       <c r="C2" t="n">
-        <v>14282</v>
+        <v>12149</v>
       </c>
       <c r="D2" t="n">
-        <v>25197</v>
+        <v>29321</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3725</v>
+        <v>3926</v>
       </c>
       <c r="C3" t="n">
-        <v>6865</v>
+        <v>7427</v>
       </c>
       <c r="D3" t="n">
-        <v>12833</v>
+        <v>16292</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2424</v>
+        <v>2865</v>
       </c>
       <c r="C4" t="n">
-        <v>4852</v>
+        <v>5244</v>
       </c>
       <c r="D4" t="n">
-        <v>7381</v>
+        <v>6995</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1914</v>
+        <v>2151</v>
       </c>
       <c r="C5" t="n">
-        <v>4498</v>
+        <v>5016</v>
       </c>
       <c r="D5" t="n">
-        <v>3241</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1280</v>
+        <v>1339</v>
       </c>
       <c r="C6" t="n">
-        <v>3487</v>
+        <v>4142</v>
       </c>
       <c r="D6" t="n">
-        <v>1387</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="C7" t="n">
-        <v>2414</v>
+        <v>2987</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="C8" t="n">
-        <v>1357</v>
+        <v>1716</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>650</v>
+        <v>792</v>
       </c>
       <c r="D9" t="n">
         <v>319</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9580</v>
+        <v>7872</v>
       </c>
       <c r="C2" t="n">
-        <v>15081</v>
+        <v>10720</v>
       </c>
       <c r="D2" t="n">
-        <v>22064</v>
+        <v>34343</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4180</v>
+        <v>4282</v>
       </c>
       <c r="C3" t="n">
-        <v>8814</v>
+        <v>8340</v>
       </c>
       <c r="D3" t="n">
-        <v>13573</v>
+        <v>16812</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2507</v>
+        <v>2790</v>
       </c>
       <c r="C4" t="n">
-        <v>5640</v>
+        <v>5985</v>
       </c>
       <c r="D4" t="n">
-        <v>7994</v>
+        <v>8121</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1896</v>
+        <v>2166</v>
       </c>
       <c r="C5" t="n">
-        <v>4510</v>
+        <v>4955</v>
       </c>
       <c r="D5" t="n">
-        <v>3707</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1417</v>
+        <v>1504</v>
       </c>
       <c r="C6" t="n">
-        <v>3838</v>
+        <v>4409</v>
       </c>
       <c r="D6" t="n">
-        <v>1635</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C7" t="n">
-        <v>2854</v>
+        <v>3438</v>
       </c>
       <c r="D7" t="n">
-        <v>789</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="C8" t="n">
-        <v>1757</v>
+        <v>2171</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>919</v>
+        <v>1118</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>424</v>
+        <v>491</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8563</v>
+        <v>7291</v>
       </c>
       <c r="C2" t="n">
-        <v>10255</v>
+        <v>7461</v>
       </c>
       <c r="D2" t="n">
-        <v>18172</v>
+        <v>28281</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4806</v>
+        <v>5040</v>
       </c>
       <c r="C3" t="n">
-        <v>12545</v>
+        <v>11706</v>
       </c>
       <c r="D3" t="n">
-        <v>14964</v>
+        <v>17827</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1751</v>
+        <v>2001</v>
       </c>
       <c r="C4" t="n">
-        <v>7469</v>
+        <v>7916</v>
       </c>
       <c r="D4" t="n">
-        <v>7780</v>
+        <v>7460</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1309</v>
+        <v>1389</v>
       </c>
       <c r="C5" t="n">
-        <v>3761</v>
+        <v>4320</v>
       </c>
       <c r="D5" t="n">
-        <v>2598</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="C6" t="n">
-        <v>2796</v>
+        <v>3369</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>1721</v>
+        <v>2127</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>900</v>
+        <v>1095</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>415</v>
+        <v>481</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4990</v>
+        <v>4466</v>
       </c>
       <c r="C2" t="n">
-        <v>4572</v>
+        <v>4146</v>
       </c>
       <c r="D2" t="n">
-        <v>12678</v>
+        <v>19712</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5442</v>
+        <v>5151</v>
       </c>
       <c r="C3" t="n">
-        <v>10446</v>
+        <v>8940</v>
       </c>
       <c r="D3" t="n">
-        <v>14538</v>
+        <v>18393</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2511</v>
+        <v>2712</v>
       </c>
       <c r="C4" t="n">
-        <v>9867</v>
+        <v>9765</v>
       </c>
       <c r="D4" t="n">
-        <v>8796</v>
+        <v>8869</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1425</v>
+        <v>1538</v>
       </c>
       <c r="C5" t="n">
-        <v>5393</v>
+        <v>5852</v>
       </c>
       <c r="D5" t="n">
-        <v>3215</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="C6" t="n">
-        <v>3272</v>
+        <v>3853</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>2167</v>
+        <v>2630</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>1170</v>
+        <v>1406</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>517</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4336</v>
+        <v>4497</v>
       </c>
       <c r="C2" t="n">
-        <v>9927</v>
+        <v>6243</v>
       </c>
       <c r="D2" t="n">
-        <v>13432</v>
+        <v>18274</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4452</v>
+        <v>4098</v>
       </c>
       <c r="C3" t="n">
-        <v>6815</v>
+        <v>6035</v>
       </c>
       <c r="D3" t="n">
-        <v>13308</v>
+        <v>17336</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3206</v>
+        <v>3211</v>
       </c>
       <c r="C4" t="n">
-        <v>9945</v>
+        <v>9173</v>
       </c>
       <c r="D4" t="n">
-        <v>9465</v>
+        <v>10153</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1677</v>
+        <v>1792</v>
       </c>
       <c r="C5" t="n">
-        <v>7437</v>
+        <v>7495</v>
       </c>
       <c r="D5" t="n">
-        <v>3974</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C6" t="n">
-        <v>4177</v>
+        <v>4718</v>
       </c>
       <c r="D6" t="n">
-        <v>1272</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="C7" t="n">
-        <v>2663</v>
+        <v>3132</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1581</v>
+        <v>1899</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>731</v>
+        <v>844</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2582</v>
+        <v>2738</v>
       </c>
       <c r="C2" t="n">
-        <v>4637</v>
+        <v>3026</v>
       </c>
       <c r="D2" t="n">
-        <v>9417</v>
+        <v>12794</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4305</v>
+        <v>4043</v>
       </c>
       <c r="C3" t="n">
-        <v>7653</v>
+        <v>5937</v>
       </c>
       <c r="D3" t="n">
-        <v>13022</v>
+        <v>17045</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3534</v>
+        <v>3519</v>
       </c>
       <c r="C4" t="n">
-        <v>9671</v>
+        <v>8898</v>
       </c>
       <c r="D4" t="n">
-        <v>10001</v>
+        <v>10986</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>9128</v>
+        <v>8992</v>
       </c>
       <c r="D5" t="n">
-        <v>4186</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>848</v>
       </c>
       <c r="C6" t="n">
-        <v>5066</v>
+        <v>5631</v>
       </c>
       <c r="D6" t="n">
-        <v>1250</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2817</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>1385</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3134</v>
+        <v>3312</v>
       </c>
       <c r="C2" t="n">
-        <v>5467</v>
+        <v>6176</v>
       </c>
       <c r="D2" t="n">
-        <v>16236</v>
+        <v>15794</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3084</v>
+        <v>3011</v>
       </c>
       <c r="C3" t="n">
-        <v>5601</v>
+        <v>4149</v>
       </c>
       <c r="D3" t="n">
-        <v>11781</v>
+        <v>15382</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3387</v>
+        <v>3287</v>
       </c>
       <c r="C4" t="n">
-        <v>8613</v>
+        <v>7433</v>
       </c>
       <c r="D4" t="n">
-        <v>10160</v>
+        <v>11582</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2186</v>
+        <v>2213</v>
       </c>
       <c r="C5" t="n">
-        <v>9265</v>
+        <v>8850</v>
       </c>
       <c r="D5" t="n">
-        <v>4896</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="C6" t="n">
-        <v>6746</v>
+        <v>6991</v>
       </c>
       <c r="D6" t="n">
-        <v>1628</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
-        <v>3725</v>
+        <v>4239</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1818</v>
+        <v>2110</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>595</v>
+        <v>654</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>131</v>
+      </c>
+      <c r="D11" t="n">
         <v>135</v>
-      </c>
-      <c r="D11" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2198</v>
+        <v>2353</v>
       </c>
       <c r="C2" t="n">
-        <v>2924</v>
+        <v>3913</v>
       </c>
       <c r="D2" t="n">
-        <v>12095</v>
+        <v>12340</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2716</v>
+        <v>2722</v>
       </c>
       <c r="C3" t="n">
-        <v>5096</v>
+        <v>4514</v>
       </c>
       <c r="D3" t="n">
-        <v>11787</v>
+        <v>14615</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3039</v>
+        <v>2956</v>
       </c>
       <c r="C4" t="n">
-        <v>7413</v>
+        <v>6160</v>
       </c>
       <c r="D4" t="n">
-        <v>10150</v>
+        <v>11815</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2412</v>
+        <v>2407</v>
       </c>
       <c r="C5" t="n">
-        <v>9196</v>
+        <v>8516</v>
       </c>
       <c r="D5" t="n">
-        <v>5350</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1286</v>
+        <v>1258</v>
       </c>
       <c r="C6" t="n">
-        <v>7781</v>
+        <v>7824</v>
       </c>
       <c r="D6" t="n">
-        <v>1938</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>4689</v>
+        <v>5148</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2287</v>
+        <v>2625</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4129</v>
+        <v>3066</v>
       </c>
       <c r="C2" t="n">
-        <v>8354</v>
+        <v>9153</v>
       </c>
       <c r="D2" t="n">
-        <v>18105</v>
+        <v>15392</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2137</v>
+        <v>2189</v>
       </c>
       <c r="C3" t="n">
-        <v>3817</v>
+        <v>3859</v>
       </c>
       <c r="D3" t="n">
-        <v>11069</v>
+        <v>13546</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2544</v>
+        <v>2501</v>
       </c>
       <c r="C4" t="n">
-        <v>6302</v>
+        <v>5309</v>
       </c>
       <c r="D4" t="n">
-        <v>10077</v>
+        <v>11718</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2414</v>
+        <v>2362</v>
       </c>
       <c r="C5" t="n">
-        <v>8302</v>
+        <v>7411</v>
       </c>
       <c r="D5" t="n">
-        <v>5832</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1524</v>
+        <v>1515</v>
       </c>
       <c r="C6" t="n">
-        <v>8246</v>
+        <v>8018</v>
       </c>
       <c r="D6" t="n">
-        <v>2339</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="C7" t="n">
-        <v>5808</v>
+        <v>6166</v>
       </c>
       <c r="D7" t="n">
-        <v>866</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3132</v>
+        <v>3464</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1179</v>
+        <v>1320</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" t="n">
         <v>92</v>
-      </c>
-      <c r="D12" t="n">
-        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7027</v>
+        <v>5709</v>
       </c>
       <c r="C2" t="n">
-        <v>9969</v>
+        <v>13177</v>
       </c>
       <c r="D2" t="n">
-        <v>8435</v>
+        <v>7011</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2984</v>
+        <v>2243</v>
       </c>
       <c r="C2" t="n">
-        <v>4878</v>
+        <v>5345</v>
       </c>
       <c r="D2" t="n">
-        <v>13471</v>
+        <v>11451</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2974</v>
+        <v>2916</v>
       </c>
       <c r="C3" t="n">
-        <v>5138</v>
+        <v>5399</v>
       </c>
       <c r="D3" t="n">
-        <v>12317</v>
+        <v>14766</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3529</v>
+        <v>3460</v>
       </c>
       <c r="C4" t="n">
-        <v>9089</v>
+        <v>7798</v>
       </c>
       <c r="D4" t="n">
-        <v>10396</v>
+        <v>11815</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1452</v>
+        <v>1421</v>
       </c>
       <c r="C5" t="n">
-        <v>11805</v>
+        <v>11138</v>
       </c>
       <c r="D5" t="n">
-        <v>5368</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="C6" t="n">
-        <v>7227</v>
+        <v>7457</v>
       </c>
       <c r="D6" t="n">
-        <v>1861</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>3069</v>
+        <v>3394</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1155</v>
+        <v>1293</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>85</v>
+      </c>
+      <c r="D11" t="n">
         <v>90</v>
-      </c>
-      <c r="D11" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6914</v>
+        <v>7113</v>
       </c>
       <c r="C2" t="n">
-        <v>4519</v>
+        <v>7788</v>
       </c>
       <c r="D2" t="n">
-        <v>16046</v>
+        <v>11748</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2985</v>
+        <v>2426</v>
       </c>
       <c r="C3" t="n">
-        <v>5024</v>
+        <v>6641</v>
       </c>
       <c r="D3" t="n">
-        <v>2056</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4783</v>
+        <v>5023</v>
       </c>
       <c r="C2" t="n">
-        <v>4821</v>
+        <v>6092</v>
       </c>
       <c r="D2" t="n">
-        <v>24034</v>
+        <v>11081</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4067</v>
+        <v>3914</v>
       </c>
       <c r="C3" t="n">
-        <v>4086</v>
+        <v>6286</v>
       </c>
       <c r="D3" t="n">
-        <v>4254</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1331</v>
+        <v>1088</v>
       </c>
       <c r="C4" t="n">
-        <v>2988</v>
+        <v>3935</v>
       </c>
       <c r="D4" t="n">
-        <v>1595</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>6384</v>
       </c>
       <c r="C2" t="n">
-        <v>8290</v>
+        <v>6738</v>
       </c>
       <c r="D2" t="n">
-        <v>26803</v>
+        <v>19207</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3642</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="n">
-        <v>3883</v>
+        <v>5409</v>
       </c>
       <c r="D3" t="n">
-        <v>7112</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2298</v>
+        <v>2125</v>
       </c>
       <c r="C4" t="n">
-        <v>3547</v>
+        <v>5124</v>
       </c>
       <c r="D4" t="n">
-        <v>2057</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>595</v>
+        <v>498</v>
       </c>
       <c r="C5" t="n">
-        <v>1729</v>
+        <v>2249</v>
       </c>
       <c r="D5" t="n">
-        <v>1222</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>76</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6009</v>
+        <v>7302</v>
       </c>
       <c r="C2" t="n">
-        <v>6794</v>
+        <v>9203</v>
       </c>
       <c r="D2" t="n">
-        <v>25085</v>
+        <v>25446</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3541</v>
+        <v>4037</v>
       </c>
       <c r="C3" t="n">
-        <v>5354</v>
+        <v>5301</v>
       </c>
       <c r="D3" t="n">
-        <v>9604</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2504</v>
+        <v>2433</v>
       </c>
       <c r="C4" t="n">
-        <v>3653</v>
+        <v>5118</v>
       </c>
       <c r="D4" t="n">
-        <v>2916</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1194</v>
+        <v>1077</v>
       </c>
       <c r="C5" t="n">
-        <v>2635</v>
+        <v>3692</v>
       </c>
       <c r="D5" t="n">
-        <v>1317</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>1009</v>
+        <v>1271</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5734</v>
+        <v>6738</v>
       </c>
       <c r="C2" t="n">
-        <v>6525</v>
+        <v>8109</v>
       </c>
       <c r="D2" t="n">
-        <v>20048</v>
+        <v>23392</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3441</v>
+        <v>4049</v>
       </c>
       <c r="C3" t="n">
-        <v>4988</v>
+        <v>5948</v>
       </c>
       <c r="D3" t="n">
-        <v>10613</v>
+        <v>8245</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1878</v>
+        <v>1978</v>
       </c>
       <c r="C4" t="n">
-        <v>3760</v>
+        <v>4267</v>
       </c>
       <c r="D4" t="n">
-        <v>3532</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>960</v>
+        <v>906</v>
       </c>
       <c r="C5" t="n">
-        <v>2306</v>
+        <v>3193</v>
       </c>
       <c r="D5" t="n">
-        <v>1247</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="C6" t="n">
-        <v>1214</v>
+        <v>1661</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>430</v>
+        <v>502</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4801</v>
+        <v>4949</v>
       </c>
       <c r="C2" t="n">
-        <v>7838</v>
+        <v>6381</v>
       </c>
       <c r="D2" t="n">
-        <v>15554</v>
+        <v>28620</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>4458</v>
       </c>
       <c r="C3" t="n">
-        <v>5060</v>
+        <v>6191</v>
       </c>
       <c r="D3" t="n">
-        <v>11416</v>
+        <v>10182</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>2636</v>
       </c>
       <c r="C4" t="n">
-        <v>4424</v>
+        <v>5137</v>
       </c>
       <c r="D4" t="n">
-        <v>4818</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C5" t="n">
-        <v>3109</v>
+        <v>3755</v>
       </c>
       <c r="D5" t="n">
-        <v>1669</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="C6" t="n">
-        <v>1805</v>
+        <v>2508</v>
       </c>
       <c r="D6" t="n">
-        <v>850</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>875</v>
+        <v>1149</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3866</v>
+        <v>5961</v>
       </c>
       <c r="C2" t="n">
-        <v>5624</v>
+        <v>6932</v>
       </c>
       <c r="D2" t="n">
-        <v>25434</v>
+        <v>33651</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3537</v>
+        <v>3875</v>
       </c>
       <c r="C3" t="n">
-        <v>5691</v>
+        <v>5456</v>
       </c>
       <c r="D3" t="n">
-        <v>11256</v>
+        <v>12496</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2625</v>
+        <v>3035</v>
       </c>
       <c r="C4" t="n">
-        <v>4692</v>
+        <v>5617</v>
       </c>
       <c r="D4" t="n">
-        <v>5938</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1588</v>
+        <v>1678</v>
       </c>
       <c r="C5" t="n">
-        <v>3763</v>
+        <v>4419</v>
       </c>
       <c r="D5" t="n">
-        <v>2176</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="C6" t="n">
-        <v>2455</v>
+        <v>3126</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>1366</v>
+        <v>1829</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>610</v>
+        <v>760</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_10_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5964</v>
+        <v>4757</v>
       </c>
       <c r="C2" t="n">
-        <v>12322</v>
+        <v>7055</v>
       </c>
       <c r="D2" t="n">
-        <v>34788</v>
+        <v>32962</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3947</v>
+        <v>2771</v>
       </c>
       <c r="C3" t="n">
-        <v>5400</v>
+        <v>6861</v>
       </c>
       <c r="D3" t="n">
-        <v>14682</v>
+        <v>14472</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2926</v>
+        <v>2313</v>
       </c>
       <c r="C4" t="n">
-        <v>5418</v>
+        <v>6381</v>
       </c>
       <c r="D4" t="n">
-        <v>5878</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2026</v>
+        <v>1630</v>
       </c>
       <c r="C5" t="n">
-        <v>4871</v>
+        <v>4524</v>
       </c>
       <c r="D5" t="n">
-        <v>2135</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1093</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>3714</v>
+        <v>3282</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>2438</v>
+        <v>2129</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1234</v>
+        <v>1104</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7435</v>
+        <v>5525</v>
       </c>
       <c r="C2" t="n">
-        <v>12149</v>
+        <v>10276</v>
       </c>
       <c r="D2" t="n">
-        <v>29321</v>
+        <v>31474</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3926</v>
+        <v>2953</v>
       </c>
       <c r="C3" t="n">
-        <v>7427</v>
+        <v>6124</v>
       </c>
       <c r="D3" t="n">
-        <v>16292</v>
+        <v>16014</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2865</v>
+        <v>2150</v>
       </c>
       <c r="C4" t="n">
-        <v>5244</v>
+        <v>6412</v>
       </c>
       <c r="D4" t="n">
-        <v>6995</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2151</v>
+        <v>1722</v>
       </c>
       <c r="C5" t="n">
-        <v>5016</v>
+        <v>5285</v>
       </c>
       <c r="D5" t="n">
-        <v>2645</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1339</v>
+        <v>1109</v>
       </c>
       <c r="C6" t="n">
-        <v>4142</v>
+        <v>3766</v>
       </c>
       <c r="D6" t="n">
-        <v>1153</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>657</v>
+        <v>564</v>
       </c>
       <c r="C7" t="n">
-        <v>2987</v>
+        <v>2636</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="C8" t="n">
-        <v>1716</v>
+        <v>1524</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>792</v>
+        <v>723</v>
       </c>
       <c r="D9" t="n">
         <v>319</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7872</v>
+        <v>6014</v>
       </c>
       <c r="C2" t="n">
-        <v>10720</v>
+        <v>9724</v>
       </c>
       <c r="D2" t="n">
-        <v>34343</v>
+        <v>41204</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4282</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>8340</v>
+        <v>6932</v>
       </c>
       <c r="D3" t="n">
-        <v>16812</v>
+        <v>16844</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2790</v>
+        <v>2103</v>
       </c>
       <c r="C4" t="n">
-        <v>5985</v>
+        <v>6092</v>
       </c>
       <c r="D4" t="n">
-        <v>8121</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2166</v>
+        <v>1693</v>
       </c>
       <c r="C5" t="n">
-        <v>4955</v>
+        <v>5651</v>
       </c>
       <c r="D5" t="n">
-        <v>3123</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1504</v>
+        <v>1233</v>
       </c>
       <c r="C6" t="n">
-        <v>4409</v>
+        <v>4308</v>
       </c>
       <c r="D6" t="n">
-        <v>1338</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>821</v>
+        <v>697</v>
       </c>
       <c r="C7" t="n">
-        <v>3438</v>
+        <v>3088</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>365</v>
+        <v>318</v>
       </c>
       <c r="C8" t="n">
-        <v>2171</v>
+        <v>1933</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>1118</v>
+        <v>1013</v>
       </c>
       <c r="D9" t="n">
         <v>332</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7291</v>
+        <v>5531</v>
       </c>
       <c r="C2" t="n">
-        <v>7461</v>
+        <v>6690</v>
       </c>
       <c r="D2" t="n">
-        <v>28281</v>
+        <v>33771</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5040</v>
+        <v>3821</v>
       </c>
       <c r="C3" t="n">
-        <v>11706</v>
+        <v>10258</v>
       </c>
       <c r="D3" t="n">
-        <v>17827</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2001</v>
+        <v>1564</v>
       </c>
       <c r="C4" t="n">
-        <v>7916</v>
+        <v>8758</v>
       </c>
       <c r="D4" t="n">
-        <v>7460</v>
+        <v>7776</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1389</v>
+        <v>1139</v>
       </c>
       <c r="C5" t="n">
-        <v>4320</v>
+        <v>4221</v>
       </c>
       <c r="D5" t="n">
-        <v>2150</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>758</v>
+        <v>644</v>
       </c>
       <c r="C6" t="n">
-        <v>3369</v>
+        <v>3026</v>
       </c>
       <c r="D6" t="n">
-        <v>710</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>2127</v>
+        <v>1894</v>
       </c>
       <c r="D7" t="n">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>1095</v>
+        <v>992</v>
       </c>
       <c r="D8" t="n">
         <v>325</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4466</v>
+        <v>3374</v>
       </c>
       <c r="C2" t="n">
-        <v>4146</v>
+        <v>3478</v>
       </c>
       <c r="D2" t="n">
-        <v>19712</v>
+        <v>23142</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5151</v>
+        <v>3918</v>
       </c>
       <c r="C3" t="n">
-        <v>8940</v>
+        <v>7850</v>
       </c>
       <c r="D3" t="n">
-        <v>18393</v>
+        <v>19215</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2712</v>
+        <v>2119</v>
       </c>
       <c r="C4" t="n">
-        <v>9765</v>
+        <v>9603</v>
       </c>
       <c r="D4" t="n">
-        <v>8869</v>
+        <v>9074</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1538</v>
+        <v>1235</v>
       </c>
       <c r="C5" t="n">
-        <v>5852</v>
+        <v>6165</v>
       </c>
       <c r="D5" t="n">
-        <v>2737</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>894</v>
+        <v>764</v>
       </c>
       <c r="C6" t="n">
-        <v>3853</v>
+        <v>3583</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>2630</v>
+        <v>2359</v>
       </c>
       <c r="D7" t="n">
-        <v>495</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>1406</v>
+        <v>1275</v>
       </c>
       <c r="D8" t="n">
         <v>334</v>
@@ -2125,10 +2125,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4497</v>
+        <v>2836</v>
       </c>
       <c r="C2" t="n">
-        <v>6243</v>
+        <v>6197</v>
       </c>
       <c r="D2" t="n">
-        <v>18274</v>
+        <v>23549</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4098</v>
+        <v>3103</v>
       </c>
       <c r="C3" t="n">
-        <v>6035</v>
+        <v>5187</v>
       </c>
       <c r="D3" t="n">
-        <v>17336</v>
+        <v>18457</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3211</v>
+        <v>2487</v>
       </c>
       <c r="C4" t="n">
-        <v>9173</v>
+        <v>8561</v>
       </c>
       <c r="D4" t="n">
-        <v>10153</v>
+        <v>10453</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>1427</v>
       </c>
       <c r="C5" t="n">
-        <v>7495</v>
+        <v>7620</v>
       </c>
       <c r="D5" t="n">
-        <v>3595</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1053</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>4718</v>
+        <v>4723</v>
       </c>
       <c r="D6" t="n">
-        <v>1107</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>465</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>3132</v>
+        <v>2873</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1899</v>
+        <v>1722</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>844</v>
+        <v>798</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2738</v>
+        <v>1707</v>
       </c>
       <c r="C2" t="n">
-        <v>3026</v>
+        <v>2956</v>
       </c>
       <c r="D2" t="n">
-        <v>12794</v>
+        <v>16424</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4043</v>
+        <v>2935</v>
       </c>
       <c r="C3" t="n">
-        <v>5937</v>
+        <v>5368</v>
       </c>
       <c r="D3" t="n">
-        <v>17045</v>
+        <v>18573</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3519</v>
+        <v>2739</v>
       </c>
       <c r="C4" t="n">
-        <v>8898</v>
+        <v>8135</v>
       </c>
       <c r="D4" t="n">
-        <v>10986</v>
+        <v>11364</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>1504</v>
       </c>
       <c r="C5" t="n">
-        <v>8992</v>
+        <v>8953</v>
       </c>
       <c r="D5" t="n">
-        <v>3828</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>725</v>
       </c>
       <c r="C6" t="n">
-        <v>5631</v>
+        <v>5645</v>
       </c>
       <c r="D6" t="n">
-        <v>1097</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>3328</v>
+        <v>3067</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3312</v>
+        <v>2529</v>
       </c>
       <c r="C2" t="n">
-        <v>6176</v>
+        <v>10364</v>
       </c>
       <c r="D2" t="n">
-        <v>15794</v>
+        <v>18770</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3011</v>
+        <v>2071</v>
       </c>
       <c r="C3" t="n">
-        <v>4149</v>
+        <v>3838</v>
       </c>
       <c r="D3" t="n">
-        <v>15382</v>
+        <v>17210</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3287</v>
+        <v>2492</v>
       </c>
       <c r="C4" t="n">
-        <v>7433</v>
+        <v>6690</v>
       </c>
       <c r="D4" t="n">
-        <v>11582</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2213</v>
+        <v>1775</v>
       </c>
       <c r="C5" t="n">
-        <v>8850</v>
+        <v>8491</v>
       </c>
       <c r="D5" t="n">
-        <v>4742</v>
+        <v>4971</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1091</v>
+        <v>926</v>
       </c>
       <c r="C6" t="n">
-        <v>6991</v>
+        <v>7015</v>
       </c>
       <c r="D6" t="n">
-        <v>1460</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>4239</v>
+        <v>4136</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2110</v>
+        <v>1940</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3173,7 +3173,7 @@
         <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2353</v>
+        <v>1749</v>
       </c>
       <c r="C2" t="n">
-        <v>3913</v>
+        <v>5580</v>
       </c>
       <c r="D2" t="n">
-        <v>12340</v>
+        <v>14455</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2722</v>
+        <v>1940</v>
       </c>
       <c r="C3" t="n">
-        <v>4514</v>
+        <v>5821</v>
       </c>
       <c r="D3" t="n">
-        <v>14615</v>
+        <v>16626</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2956</v>
+        <v>2167</v>
       </c>
       <c r="C4" t="n">
-        <v>6160</v>
+        <v>5556</v>
       </c>
       <c r="D4" t="n">
-        <v>11815</v>
+        <v>12507</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2407</v>
+        <v>1910</v>
       </c>
       <c r="C5" t="n">
-        <v>8516</v>
+        <v>8000</v>
       </c>
       <c r="D5" t="n">
-        <v>5411</v>
+        <v>5623</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1258</v>
+        <v>1074</v>
       </c>
       <c r="C6" t="n">
-        <v>7824</v>
+        <v>7751</v>
       </c>
       <c r="D6" t="n">
-        <v>1723</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="C7" t="n">
-        <v>5148</v>
+        <v>5095</v>
       </c>
       <c r="D7" t="n">
-        <v>670</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2625</v>
+        <v>2464</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3372,7 +3372,7 @@
         <v>715</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3470,7 +3470,7 @@
         <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3066</v>
+        <v>3056</v>
       </c>
       <c r="C2" t="n">
-        <v>9153</v>
+        <v>6139</v>
       </c>
       <c r="D2" t="n">
-        <v>15392</v>
+        <v>14738</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2189</v>
+        <v>1578</v>
       </c>
       <c r="C3" t="n">
-        <v>3859</v>
+        <v>5149</v>
       </c>
       <c r="D3" t="n">
-        <v>13546</v>
+        <v>15301</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>1815</v>
       </c>
       <c r="C4" t="n">
-        <v>5309</v>
+        <v>5549</v>
       </c>
       <c r="D4" t="n">
-        <v>11718</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2362</v>
+        <v>1844</v>
       </c>
       <c r="C5" t="n">
-        <v>7411</v>
+        <v>6871</v>
       </c>
       <c r="D5" t="n">
-        <v>6107</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1515</v>
+        <v>1253</v>
       </c>
       <c r="C6" t="n">
-        <v>8018</v>
+        <v>7780</v>
       </c>
       <c r="D6" t="n">
-        <v>2161</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>6166</v>
+        <v>6056</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>3464</v>
+        <v>3389</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1320</v>
+        <v>1263</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5709</v>
+        <v>3888</v>
       </c>
       <c r="C2" t="n">
-        <v>13177</v>
+        <v>10672</v>
       </c>
       <c r="D2" t="n">
-        <v>7011</v>
+        <v>6972</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2243</v>
+        <v>2207</v>
       </c>
       <c r="C2" t="n">
-        <v>5345</v>
+        <v>3585</v>
       </c>
       <c r="D2" t="n">
-        <v>11451</v>
+        <v>10965</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2916</v>
+        <v>2192</v>
       </c>
       <c r="C3" t="n">
-        <v>5399</v>
+        <v>5824</v>
       </c>
       <c r="D3" t="n">
-        <v>14766</v>
+        <v>16369</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3460</v>
+        <v>2613</v>
       </c>
       <c r="C4" t="n">
-        <v>7798</v>
+        <v>8014</v>
       </c>
       <c r="D4" t="n">
-        <v>11815</v>
+        <v>12886</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1421</v>
+        <v>1191</v>
       </c>
       <c r="C5" t="n">
-        <v>11138</v>
+        <v>10529</v>
       </c>
       <c r="D5" t="n">
-        <v>5477</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>466</v>
+        <v>401</v>
       </c>
       <c r="C6" t="n">
-        <v>7457</v>
+        <v>7383</v>
       </c>
       <c r="D6" t="n">
-        <v>1707</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>3394</v>
+        <v>3321</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1293</v>
+        <v>1237</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7113</v>
+        <v>6335</v>
       </c>
       <c r="C2" t="n">
-        <v>7788</v>
+        <v>6944</v>
       </c>
       <c r="D2" t="n">
-        <v>11748</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2426</v>
+        <v>1654</v>
       </c>
       <c r="C3" t="n">
-        <v>6641</v>
+        <v>5378</v>
       </c>
       <c r="D3" t="n">
-        <v>1817</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5023</v>
+        <v>5015</v>
       </c>
       <c r="C2" t="n">
-        <v>6092</v>
+        <v>5190</v>
       </c>
       <c r="D2" t="n">
-        <v>11081</v>
+        <v>17090</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3914</v>
+        <v>3275</v>
       </c>
       <c r="C3" t="n">
-        <v>6286</v>
+        <v>5402</v>
       </c>
       <c r="D3" t="n">
-        <v>3351</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1088</v>
+        <v>752</v>
       </c>
       <c r="C4" t="n">
-        <v>3935</v>
+        <v>3193</v>
       </c>
       <c r="D4" t="n">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6384</v>
+        <v>4709</v>
       </c>
       <c r="C2" t="n">
-        <v>6738</v>
+        <v>7011</v>
       </c>
       <c r="D2" t="n">
-        <v>19207</v>
+        <v>17444</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3669</v>
+        <v>3388</v>
       </c>
       <c r="C3" t="n">
-        <v>5409</v>
+        <v>4575</v>
       </c>
       <c r="D3" t="n">
-        <v>4346</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2125</v>
+        <v>1706</v>
       </c>
       <c r="C4" t="n">
-        <v>5124</v>
+        <v>4377</v>
       </c>
       <c r="D4" t="n">
-        <v>1846</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>498</v>
+        <v>363</v>
       </c>
       <c r="C5" t="n">
-        <v>2249</v>
+        <v>1842</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7302</v>
+        <v>5167</v>
       </c>
       <c r="C2" t="n">
-        <v>9203</v>
+        <v>7101</v>
       </c>
       <c r="D2" t="n">
-        <v>25446</v>
+        <v>24164</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4037</v>
+        <v>3300</v>
       </c>
       <c r="C3" t="n">
-        <v>5301</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>6298</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2433</v>
+        <v>2156</v>
       </c>
       <c r="C4" t="n">
-        <v>5118</v>
+        <v>4392</v>
       </c>
       <c r="D4" t="n">
-        <v>2245</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1077</v>
+        <v>841</v>
       </c>
       <c r="C5" t="n">
-        <v>3692</v>
+        <v>3100</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="C6" t="n">
-        <v>1271</v>
+        <v>1081</v>
       </c>
       <c r="D6" t="n">
         <v>948</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6738</v>
+        <v>5215</v>
       </c>
       <c r="C2" t="n">
-        <v>8109</v>
+        <v>8874</v>
       </c>
       <c r="D2" t="n">
-        <v>23392</v>
+        <v>26373</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4049</v>
+        <v>3057</v>
       </c>
       <c r="C3" t="n">
-        <v>5948</v>
+        <v>5004</v>
       </c>
       <c r="D3" t="n">
-        <v>8245</v>
+        <v>8426</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1978</v>
+        <v>1681</v>
       </c>
       <c r="C4" t="n">
-        <v>4267</v>
+        <v>3905</v>
       </c>
       <c r="D4" t="n">
-        <v>2543</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>906</v>
+        <v>779</v>
       </c>
       <c r="C5" t="n">
-        <v>3193</v>
+        <v>2728</v>
       </c>
       <c r="D5" t="n">
-        <v>1126</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>318</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>1661</v>
+        <v>1413</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>502</v>
+        <v>451</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4949</v>
+        <v>4049</v>
       </c>
       <c r="C2" t="n">
-        <v>6381</v>
+        <v>10719</v>
       </c>
       <c r="D2" t="n">
-        <v>28620</v>
+        <v>30308</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4458</v>
+        <v>3435</v>
       </c>
       <c r="C3" t="n">
-        <v>6191</v>
+        <v>6249</v>
       </c>
       <c r="D3" t="n">
-        <v>10182</v>
+        <v>10820</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2636</v>
+        <v>2082</v>
       </c>
       <c r="C4" t="n">
-        <v>5137</v>
+        <v>4488</v>
       </c>
       <c r="D4" t="n">
-        <v>3615</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1269</v>
+        <v>1097</v>
       </c>
       <c r="C5" t="n">
-        <v>3755</v>
+        <v>3334</v>
       </c>
       <c r="D5" t="n">
-        <v>1353</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>565</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>2508</v>
+        <v>2152</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>1149</v>
+        <v>997</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5961</v>
+        <v>3692</v>
       </c>
       <c r="C2" t="n">
-        <v>6932</v>
+        <v>8197</v>
       </c>
       <c r="D2" t="n">
-        <v>33651</v>
+        <v>28570</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3875</v>
+        <v>3079</v>
       </c>
       <c r="C3" t="n">
-        <v>5456</v>
+        <v>7518</v>
       </c>
       <c r="D3" t="n">
-        <v>12496</v>
+        <v>13159</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3035</v>
+        <v>2374</v>
       </c>
       <c r="C4" t="n">
-        <v>5617</v>
+        <v>5392</v>
       </c>
       <c r="D4" t="n">
-        <v>4668</v>
+        <v>5019</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1678</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>4419</v>
+        <v>3896</v>
       </c>
       <c r="D5" t="n">
-        <v>1724</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>825</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>3126</v>
+        <v>2751</v>
       </c>
       <c r="D6" t="n">
-        <v>893</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="C7" t="n">
-        <v>1829</v>
+        <v>1586</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>760</v>
+        <v>678</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_10_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4757</v>
+        <v>1174</v>
       </c>
       <c r="C2" t="n">
-        <v>7055</v>
+        <v>1512</v>
       </c>
       <c r="D2" t="n">
-        <v>32962</v>
+        <v>14854</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2771</v>
+        <v>2355</v>
       </c>
       <c r="C3" t="n">
-        <v>6861</v>
+        <v>3871</v>
       </c>
       <c r="D3" t="n">
-        <v>14472</v>
+        <v>15350</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2313</v>
+        <v>1783</v>
       </c>
       <c r="C4" t="n">
-        <v>6381</v>
+        <v>6059</v>
       </c>
       <c r="D4" t="n">
-        <v>6224</v>
+        <v>6964</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1630</v>
+        <v>938</v>
       </c>
       <c r="C5" t="n">
-        <v>4524</v>
+        <v>4959</v>
       </c>
       <c r="D5" t="n">
-        <v>2305</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>377</v>
       </c>
       <c r="C6" t="n">
-        <v>3282</v>
+        <v>2225</v>
       </c>
       <c r="D6" t="n">
-        <v>1046</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>2129</v>
+        <v>792</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1104</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>458</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5525</v>
+        <v>1280</v>
       </c>
       <c r="C2" t="n">
-        <v>10276</v>
+        <v>6100</v>
       </c>
       <c r="D2" t="n">
-        <v>31474</v>
+        <v>12460</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2953</v>
+        <v>1524</v>
       </c>
       <c r="C3" t="n">
-        <v>6124</v>
+        <v>2287</v>
       </c>
       <c r="D3" t="n">
-        <v>16014</v>
+        <v>14193</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2150</v>
+        <v>1788</v>
       </c>
       <c r="C4" t="n">
-        <v>6412</v>
+        <v>4793</v>
       </c>
       <c r="D4" t="n">
-        <v>7380</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>1173</v>
       </c>
       <c r="C5" t="n">
-        <v>5285</v>
+        <v>5473</v>
       </c>
       <c r="D5" t="n">
-        <v>2814</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1109</v>
+        <v>569</v>
       </c>
       <c r="C6" t="n">
-        <v>3766</v>
+        <v>3539</v>
       </c>
       <c r="D6" t="n">
-        <v>1225</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>564</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>2636</v>
+        <v>1487</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1524</v>
+        <v>559</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>723</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>314</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6014</v>
+        <v>684</v>
       </c>
       <c r="C2" t="n">
-        <v>9724</v>
+        <v>2534</v>
       </c>
       <c r="D2" t="n">
-        <v>41204</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>1399</v>
       </c>
       <c r="C3" t="n">
-        <v>6932</v>
+        <v>3686</v>
       </c>
       <c r="D3" t="n">
-        <v>16844</v>
+        <v>13585</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2103</v>
+        <v>1932</v>
       </c>
       <c r="C4" t="n">
-        <v>6092</v>
+        <v>4213</v>
       </c>
       <c r="D4" t="n">
-        <v>8328</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1693</v>
+        <v>1189</v>
       </c>
       <c r="C5" t="n">
-        <v>5651</v>
+        <v>5964</v>
       </c>
       <c r="D5" t="n">
-        <v>3385</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1233</v>
+        <v>435</v>
       </c>
       <c r="C6" t="n">
-        <v>4308</v>
+        <v>4439</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>697</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3088</v>
+        <v>1414</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1933</v>
+        <v>502</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1013</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>462</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5531</v>
+        <v>729</v>
       </c>
       <c r="C2" t="n">
-        <v>6690</v>
+        <v>2722</v>
       </c>
       <c r="D2" t="n">
-        <v>33771</v>
+        <v>12385</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3821</v>
+        <v>919</v>
       </c>
       <c r="C3" t="n">
-        <v>10258</v>
+        <v>2727</v>
       </c>
       <c r="D3" t="n">
-        <v>17920</v>
+        <v>11841</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1564</v>
+        <v>1495</v>
       </c>
       <c r="C4" t="n">
-        <v>8758</v>
+        <v>3887</v>
       </c>
       <c r="D4" t="n">
-        <v>7776</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1139</v>
+        <v>1378</v>
       </c>
       <c r="C5" t="n">
-        <v>4221</v>
+        <v>5023</v>
       </c>
       <c r="D5" t="n">
-        <v>2291</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="C6" t="n">
-        <v>3026</v>
+        <v>5154</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>1894</v>
+        <v>2804</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>891</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>452</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
         <v>50</v>
-      </c>
-      <c r="D15" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3374</v>
+        <v>457</v>
       </c>
       <c r="C2" t="n">
-        <v>3478</v>
+        <v>2556</v>
       </c>
       <c r="D2" t="n">
-        <v>23142</v>
+        <v>9992</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3918</v>
+        <v>740</v>
       </c>
       <c r="C3" t="n">
-        <v>7850</v>
+        <v>2467</v>
       </c>
       <c r="D3" t="n">
-        <v>19215</v>
+        <v>11232</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2119</v>
+        <v>1198</v>
       </c>
       <c r="C4" t="n">
-        <v>9603</v>
+        <v>3372</v>
       </c>
       <c r="D4" t="n">
-        <v>9074</v>
+        <v>9908</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1235</v>
+        <v>1400</v>
       </c>
       <c r="C5" t="n">
-        <v>6165</v>
+        <v>4631</v>
       </c>
       <c r="D5" t="n">
-        <v>2949</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>764</v>
+        <v>823</v>
       </c>
       <c r="C6" t="n">
-        <v>3583</v>
+        <v>5317</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>197</v>
       </c>
       <c r="C7" t="n">
-        <v>2359</v>
+        <v>3736</v>
       </c>
       <c r="D7" t="n">
-        <v>510</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1275</v>
+        <v>1362</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2836</v>
+        <v>1654</v>
       </c>
       <c r="C2" t="n">
-        <v>6197</v>
+        <v>6126</v>
       </c>
       <c r="D2" t="n">
-        <v>23549</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3103</v>
+        <v>522</v>
       </c>
       <c r="C3" t="n">
-        <v>5187</v>
+        <v>2223</v>
       </c>
       <c r="D3" t="n">
-        <v>18457</v>
+        <v>10388</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2487</v>
+        <v>887</v>
       </c>
       <c r="C4" t="n">
-        <v>8561</v>
+        <v>2858</v>
       </c>
       <c r="D4" t="n">
-        <v>10453</v>
+        <v>9822</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1427</v>
+        <v>1225</v>
       </c>
       <c r="C5" t="n">
-        <v>7620</v>
+        <v>3942</v>
       </c>
       <c r="D5" t="n">
-        <v>3800</v>
+        <v>5415</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>4723</v>
+        <v>5007</v>
       </c>
       <c r="D6" t="n">
-        <v>1181</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="C7" t="n">
-        <v>2873</v>
+        <v>4416</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>1722</v>
+        <v>2351</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1707</v>
+        <v>1098</v>
       </c>
       <c r="C2" t="n">
-        <v>2956</v>
+        <v>3137</v>
       </c>
       <c r="D2" t="n">
-        <v>16424</v>
+        <v>8323</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2935</v>
+        <v>911</v>
       </c>
       <c r="C3" t="n">
-        <v>5368</v>
+        <v>3514</v>
       </c>
       <c r="D3" t="n">
-        <v>18573</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2739</v>
+        <v>1555</v>
       </c>
       <c r="C4" t="n">
-        <v>8135</v>
+        <v>4111</v>
       </c>
       <c r="D4" t="n">
-        <v>11364</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1504</v>
+        <v>991</v>
       </c>
       <c r="C5" t="n">
-        <v>8953</v>
+        <v>6431</v>
       </c>
       <c r="D5" t="n">
-        <v>4039</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>725</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>5645</v>
+        <v>5603</v>
       </c>
       <c r="D6" t="n">
-        <v>1166</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>3067</v>
+        <v>2303</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>787</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2529</v>
+        <v>583</v>
       </c>
       <c r="C2" t="n">
-        <v>10364</v>
+        <v>1743</v>
       </c>
       <c r="D2" t="n">
-        <v>18770</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2071</v>
+        <v>830</v>
       </c>
       <c r="C3" t="n">
-        <v>3838</v>
+        <v>2924</v>
       </c>
       <c r="D3" t="n">
-        <v>17210</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2492</v>
+        <v>1046</v>
       </c>
       <c r="C4" t="n">
-        <v>6690</v>
+        <v>3572</v>
       </c>
       <c r="D4" t="n">
-        <v>12125</v>
+        <v>9666</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1775</v>
+        <v>895</v>
       </c>
       <c r="C5" t="n">
-        <v>8491</v>
+        <v>4712</v>
       </c>
       <c r="D5" t="n">
-        <v>4971</v>
+        <v>5162</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>355</v>
       </c>
       <c r="C6" t="n">
-        <v>7015</v>
+        <v>4981</v>
       </c>
       <c r="D6" t="n">
-        <v>1536</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>4136</v>
+        <v>2745</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1940</v>
+        <v>907</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>632</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1749</v>
+        <v>610</v>
       </c>
       <c r="C2" t="n">
-        <v>5580</v>
+        <v>8493</v>
       </c>
       <c r="D2" t="n">
-        <v>14455</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1940</v>
+        <v>593</v>
       </c>
       <c r="C3" t="n">
-        <v>5821</v>
+        <v>1959</v>
       </c>
       <c r="D3" t="n">
-        <v>16626</v>
+        <v>8781</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2167</v>
+        <v>818</v>
       </c>
       <c r="C4" t="n">
-        <v>5556</v>
+        <v>3124</v>
       </c>
       <c r="D4" t="n">
-        <v>12507</v>
+        <v>9456</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1910</v>
+        <v>881</v>
       </c>
       <c r="C5" t="n">
-        <v>8000</v>
+        <v>4024</v>
       </c>
       <c r="D5" t="n">
-        <v>5623</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1074</v>
+        <v>557</v>
       </c>
       <c r="C6" t="n">
-        <v>7751</v>
+        <v>4830</v>
       </c>
       <c r="D6" t="n">
-        <v>1859</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>5095</v>
+        <v>3883</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>2464</v>
+        <v>1816</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>715</v>
+        <v>582</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3056</v>
+        <v>843</v>
       </c>
       <c r="C2" t="n">
-        <v>6139</v>
+        <v>9085</v>
       </c>
       <c r="D2" t="n">
-        <v>14738</v>
+        <v>13813</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1578</v>
+        <v>497</v>
       </c>
       <c r="C3" t="n">
-        <v>5149</v>
+        <v>4632</v>
       </c>
       <c r="D3" t="n">
-        <v>15301</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1815</v>
+        <v>622</v>
       </c>
       <c r="C4" t="n">
-        <v>5549</v>
+        <v>2432</v>
       </c>
       <c r="D4" t="n">
-        <v>12719</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1844</v>
+        <v>770</v>
       </c>
       <c r="C5" t="n">
-        <v>6871</v>
+        <v>3473</v>
       </c>
       <c r="D5" t="n">
-        <v>6377</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1253</v>
+        <v>653</v>
       </c>
       <c r="C6" t="n">
-        <v>7780</v>
+        <v>4375</v>
       </c>
       <c r="D6" t="n">
-        <v>2304</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>6056</v>
+        <v>4345</v>
       </c>
       <c r="D7" t="n">
-        <v>833</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>3389</v>
+        <v>2787</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1263</v>
+        <v>1138</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3888</v>
+        <v>7082</v>
       </c>
       <c r="C2" t="n">
-        <v>10672</v>
+        <v>13190</v>
       </c>
       <c r="D2" t="n">
-        <v>6972</v>
+        <v>16314</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2207</v>
+        <v>979</v>
       </c>
       <c r="C2" t="n">
-        <v>3585</v>
+        <v>8723</v>
       </c>
       <c r="D2" t="n">
-        <v>10965</v>
+        <v>17713</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2192</v>
+        <v>528</v>
       </c>
       <c r="C3" t="n">
-        <v>5824</v>
+        <v>5885</v>
       </c>
       <c r="D3" t="n">
-        <v>16369</v>
+        <v>8086</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2613</v>
+        <v>490</v>
       </c>
       <c r="C4" t="n">
-        <v>8014</v>
+        <v>3458</v>
       </c>
       <c r="D4" t="n">
-        <v>12886</v>
+        <v>8478</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1191</v>
+        <v>651</v>
       </c>
       <c r="C5" t="n">
-        <v>10529</v>
+        <v>2911</v>
       </c>
       <c r="D5" t="n">
-        <v>5742</v>
+        <v>6537</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>401</v>
+        <v>651</v>
       </c>
       <c r="C6" t="n">
-        <v>7383</v>
+        <v>3882</v>
       </c>
       <c r="D6" t="n">
-        <v>1816</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>3321</v>
+        <v>4356</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>1237</v>
+        <v>3457</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>1805</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>674</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6335</v>
+        <v>6676</v>
       </c>
       <c r="C2" t="n">
-        <v>6944</v>
+        <v>10268</v>
       </c>
       <c r="D2" t="n">
-        <v>11950</v>
+        <v>19728</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1654</v>
+        <v>2281</v>
       </c>
       <c r="C3" t="n">
-        <v>5378</v>
+        <v>5208</v>
       </c>
       <c r="D3" t="n">
-        <v>1810</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5015</v>
+        <v>4089</v>
       </c>
       <c r="C2" t="n">
-        <v>5190</v>
+        <v>6211</v>
       </c>
       <c r="D2" t="n">
-        <v>17090</v>
+        <v>26936</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3275</v>
+        <v>3778</v>
       </c>
       <c r="C3" t="n">
-        <v>5402</v>
+        <v>7057</v>
       </c>
       <c r="D3" t="n">
-        <v>3380</v>
+        <v>5594</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>752</v>
+        <v>1078</v>
       </c>
       <c r="C4" t="n">
-        <v>3193</v>
+        <v>3248</v>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4709</v>
+        <v>2311</v>
       </c>
       <c r="C2" t="n">
-        <v>7011</v>
+        <v>4490</v>
       </c>
       <c r="D2" t="n">
-        <v>17444</v>
+        <v>28897</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3388</v>
+        <v>3245</v>
       </c>
       <c r="C3" t="n">
-        <v>4575</v>
+        <v>5673</v>
       </c>
       <c r="D3" t="n">
-        <v>5330</v>
+        <v>8767</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1706</v>
+        <v>2110</v>
       </c>
       <c r="C4" t="n">
-        <v>4377</v>
+        <v>5410</v>
       </c>
       <c r="D4" t="n">
-        <v>1851</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>363</v>
+        <v>498</v>
       </c>
       <c r="C5" t="n">
-        <v>1842</v>
+        <v>1925</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5167</v>
+        <v>3328</v>
       </c>
       <c r="C2" t="n">
-        <v>7101</v>
+        <v>3383</v>
       </c>
       <c r="D2" t="n">
-        <v>24164</v>
+        <v>25692</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3300</v>
+        <v>2325</v>
       </c>
       <c r="C3" t="n">
-        <v>5073</v>
+        <v>4370</v>
       </c>
       <c r="D3" t="n">
-        <v>6796</v>
+        <v>11356</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2156</v>
+        <v>2279</v>
       </c>
       <c r="C4" t="n">
-        <v>4392</v>
+        <v>5443</v>
       </c>
       <c r="D4" t="n">
-        <v>2429</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>841</v>
+        <v>1098</v>
       </c>
       <c r="C5" t="n">
-        <v>3100</v>
+        <v>3758</v>
       </c>
       <c r="D5" t="n">
-        <v>1267</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>1081</v>
+        <v>1122</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5215</v>
+        <v>2377</v>
       </c>
       <c r="C2" t="n">
-        <v>8874</v>
+        <v>3341</v>
       </c>
       <c r="D2" t="n">
-        <v>26373</v>
+        <v>26226</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3057</v>
+        <v>2294</v>
       </c>
       <c r="C3" t="n">
-        <v>5004</v>
+        <v>3376</v>
       </c>
       <c r="D3" t="n">
-        <v>8426</v>
+        <v>12735</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1681</v>
+        <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>3905</v>
+        <v>4763</v>
       </c>
       <c r="D4" t="n">
-        <v>2749</v>
+        <v>4883</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>779</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>2728</v>
+        <v>4537</v>
       </c>
       <c r="D5" t="n">
-        <v>1147</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>1413</v>
+        <v>2400</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>451</v>
+        <v>688</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4049</v>
+        <v>2537</v>
       </c>
       <c r="C2" t="n">
-        <v>10719</v>
+        <v>5515</v>
       </c>
       <c r="D2" t="n">
-        <v>30308</v>
+        <v>27758</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3435</v>
+        <v>1931</v>
       </c>
       <c r="C3" t="n">
-        <v>6249</v>
+        <v>2951</v>
       </c>
       <c r="D3" t="n">
-        <v>10820</v>
+        <v>13713</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2082</v>
+        <v>1844</v>
       </c>
       <c r="C4" t="n">
-        <v>4488</v>
+        <v>3939</v>
       </c>
       <c r="D4" t="n">
-        <v>3783</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1097</v>
+        <v>1497</v>
       </c>
       <c r="C5" t="n">
-        <v>3334</v>
+        <v>4551</v>
       </c>
       <c r="D5" t="n">
-        <v>1435</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>472</v>
+        <v>860</v>
       </c>
       <c r="C6" t="n">
-        <v>2152</v>
+        <v>3360</v>
       </c>
       <c r="D6" t="n">
-        <v>825</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>997</v>
+        <v>1452</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>348</v>
+        <v>470</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3692</v>
+        <v>2358</v>
       </c>
       <c r="C2" t="n">
-        <v>8197</v>
+        <v>3485</v>
       </c>
       <c r="D2" t="n">
-        <v>28570</v>
+        <v>22025</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3079</v>
+        <v>2887</v>
       </c>
       <c r="C3" t="n">
-        <v>7518</v>
+        <v>5120</v>
       </c>
       <c r="D3" t="n">
-        <v>13159</v>
+        <v>15064</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2374</v>
+        <v>1383</v>
       </c>
       <c r="C4" t="n">
-        <v>5392</v>
+        <v>6789</v>
       </c>
       <c r="D4" t="n">
-        <v>5019</v>
+        <v>5458</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>794</v>
       </c>
       <c r="C5" t="n">
-        <v>3896</v>
+        <v>3292</v>
       </c>
       <c r="D5" t="n">
-        <v>1805</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>2751</v>
+        <v>1422</v>
       </c>
       <c r="D6" t="n">
-        <v>924</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>1586</v>
+        <v>460</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>678</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
